--- a/Assets/Game/Content/Data/EnemyTable.xlsx
+++ b/Assets/Game/Content/Data/EnemyTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26327"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GameProjects\Alchemy\Assets\Game\Content\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NLA2.0\Assets\Game\Content\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98C77C66-B69F-4B58-A272-39B7C300AE5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{272D0C2A-CD77-4404-B34A-438F10F318B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="1515" windowWidth="21345" windowHeight="19365" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="630" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="38">
   <si>
     <t>Id</t>
   </si>
@@ -91,31 +91,31 @@
   </si>
   <si>
     <t>[1, 10, 0]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>[3, 35, 0]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>[4, 40, 0]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>[5, 55, 0]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>[6, 60, 0]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>TestBoss</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>[1, 15, 0]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Test2</t>
@@ -134,39 +134,50 @@
   </si>
   <si>
     <t>[2, 20, 0]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>[3, 30, 0]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>[4, 45, 0]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>[5, 50, 0]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Test</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>[6, 25, 0]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enemy/Enemy02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -205,12 +216,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -484,16 +496,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
-    <col min="2" max="2" width="19.75" customWidth="1"/>
-    <col min="3" max="3" width="25.375" customWidth="1"/>
-    <col min="4" max="4" width="38.875" customWidth="1"/>
+    <col min="2" max="2" width="19.69921875" customWidth="1"/>
+    <col min="3" max="3" width="25.3984375" customWidth="1"/>
+    <col min="4" max="4" width="38.8984375" customWidth="1"/>
     <col min="5" max="5" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -510,7 +522,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -527,7 +539,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -541,7 +553,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -555,7 +567,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
         <v>35</v>
       </c>
@@ -568,11 +580,11 @@
       <c r="D5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E5" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -589,7 +601,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
         <v>26</v>
       </c>
@@ -606,7 +618,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
         <v>27</v>
       </c>
@@ -623,7 +635,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -640,7 +652,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
         <v>28</v>
       </c>
@@ -657,7 +669,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
@@ -674,7 +686,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
         <v>29</v>
       </c>
@@ -691,7 +703,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
         <v>17</v>
       </c>
@@ -708,7 +720,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5">
       <c r="A14" s="1" t="s">
         <v>30</v>
       </c>
@@ -725,7 +737,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -743,7 +755,8 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>